--- a/real_vs_previsto_ultimas_12h.xlsx
+++ b/real_vs_previsto_ultimas_12h.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,34 +433,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Real (m)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Previsto (m)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Erro (m)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Erro Abs (m)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46067</v>
       </c>
       <c r="B2" t="n">
@@ -465,7 +477,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46067.01041666666</v>
       </c>
       <c r="B3" t="n">
@@ -482,7 +494,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46067.02083333334</v>
       </c>
       <c r="B4" t="n">
@@ -499,7 +511,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46067.03125</v>
       </c>
       <c r="B5" t="n">
@@ -516,7 +528,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46067.04166666666</v>
       </c>
       <c r="B6" t="n">
@@ -533,7 +545,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46067.05208333334</v>
       </c>
       <c r="B7" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46067.0625</v>
       </c>
       <c r="B8" t="n">
@@ -567,7 +579,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46067.07291666666</v>
       </c>
       <c r="B9" t="n">
@@ -584,7 +596,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46067.08333333334</v>
       </c>
       <c r="B10" t="n">
@@ -601,7 +613,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46067.09375</v>
       </c>
       <c r="B11" t="n">
@@ -618,7 +630,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46067.10416666666</v>
       </c>
       <c r="B12" t="n">
@@ -635,7 +647,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46067.11458333334</v>
       </c>
       <c r="B13" t="n">
@@ -652,7 +664,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46067.125</v>
       </c>
       <c r="B14" t="n">
@@ -669,7 +681,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46067.13541666666</v>
       </c>
       <c r="B15" t="n">
@@ -686,7 +698,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46067.14583333334</v>
       </c>
       <c r="B16" t="n">
@@ -703,7 +715,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46067.15625</v>
       </c>
       <c r="B17" t="n">
@@ -720,7 +732,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46067.16666666666</v>
       </c>
       <c r="B18" t="n">
@@ -737,7 +749,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46067.17708333334</v>
       </c>
       <c r="B19" t="n">
@@ -754,7 +766,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46067.1875</v>
       </c>
       <c r="B20" t="n">
@@ -771,7 +783,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46067.19791666666</v>
       </c>
       <c r="B21" t="n">
@@ -788,7 +800,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46067.20833333334</v>
       </c>
       <c r="B22" t="n">
@@ -805,7 +817,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46067.21875</v>
       </c>
       <c r="B23" t="n">
@@ -822,7 +834,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46067.22916666666</v>
       </c>
       <c r="B24" t="n">
@@ -839,7 +851,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46067.23958333334</v>
       </c>
       <c r="B25" t="n">
@@ -856,7 +868,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46067.25</v>
       </c>
       <c r="B26" t="n">
@@ -873,7 +885,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46067.26041666666</v>
       </c>
       <c r="B27" t="n">
@@ -890,7 +902,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46067.27083333334</v>
       </c>
       <c r="B28" t="n">
@@ -907,7 +919,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46067.28125</v>
       </c>
       <c r="B29" t="n">
@@ -924,7 +936,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46067.29166666666</v>
       </c>
       <c r="B30" t="n">
@@ -941,7 +953,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46067.30208333334</v>
       </c>
       <c r="B31" t="n">
@@ -958,7 +970,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46067.3125</v>
       </c>
       <c r="B32" t="n">
@@ -975,7 +987,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46067.32291666666</v>
       </c>
       <c r="B33" t="n">
@@ -992,7 +1004,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46067.33333333334</v>
       </c>
       <c r="B34" t="n">
@@ -1009,7 +1021,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46067.34375</v>
       </c>
       <c r="B35" t="n">
@@ -1026,7 +1038,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46067.35416666666</v>
       </c>
       <c r="B36" t="n">
@@ -1043,7 +1055,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46067.36458333334</v>
       </c>
       <c r="B37" t="n">
@@ -1060,7 +1072,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46067.375</v>
       </c>
       <c r="B38" t="n">
@@ -1077,7 +1089,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46067.38541666666</v>
       </c>
       <c r="B39" t="n">
@@ -1094,7 +1106,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46067.39583333334</v>
       </c>
       <c r="B40" t="n">
@@ -1111,7 +1123,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>46067.40625</v>
       </c>
       <c r="B41" t="n">
@@ -1128,7 +1140,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>46067.41666666666</v>
       </c>
       <c r="B42" t="n">
@@ -1145,7 +1157,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46067.42708333334</v>
       </c>
       <c r="B43" t="n">
@@ -1162,7 +1174,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46067.4375</v>
       </c>
       <c r="B44" t="n">
@@ -1179,7 +1191,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46067.44791666666</v>
       </c>
       <c r="B45" t="n">
@@ -1196,7 +1208,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>46067.45833333334</v>
       </c>
       <c r="B46" t="n">
@@ -1213,7 +1225,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>46067.46875</v>
       </c>
       <c r="B47" t="n">
@@ -1230,7 +1242,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46067.47916666666</v>
       </c>
       <c r="B48" t="n">
@@ -1247,7 +1259,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>46067.48958333334</v>
       </c>
       <c r="B49" t="n">
@@ -1264,7 +1276,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46067.5</v>
       </c>
       <c r="B50" t="n">
